--- a/260808.xlsx
+++ b/260808.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7221F190-BF0B-4249-ADD4-01628A8091B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525E28A2-1BEA-4958-8538-651BC1E1BEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10470" yWindow="2250" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10570" yWindow="4110" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
-    <sheet name="SheetX" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId3"/>
+    <sheet name="SheetX" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Hahne: Zu Gast im Deutschlandfunk Interview der Woche ist Bernhard Mattes, Vorsitzender der Geschäftsführung von Ford Deutschland.
 Herr Mattes, nicht nur das Auto wird sich in Zukunft verändern, sondern auch wie es gebaut wird, Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Industrie 4.0"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , also die Vernetzung der gesamten Wertschöpfungskette.
@@ -335,15 +334,6 @@
 Reker: Ja, wir werden natürlich die Erfahrungen, die wir aus dem vorigen Jahr mitgenommen haben, in Konzepte für das nächste Jahr bringen und uns genau überlegen, wie man das machen kann.
 Wir haben seitdem ja auch andere Großveranstaltungen erfolgreich durchgeführt – ich denke nur an Cologne Pride, also Christopher Street Day, ich denke an den Karneval.
 Und – ja – ich werden den Polizeipräsidenten einladen, mit mir Silvester zu feiern, dann sitzen wir schon mal zusammen.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>feststeht –, aber über 
-in Randgebieten sein?
-Reker: Zum Beispiel.
-Küpper: Flüchtlingsthematik noch einmal einen neuen Schwung bekommen hat.
-Ihr Kollege aus Tübingen, Boris Palmer, der hat gesagt.
-Reker: Die Kommunen sind immer die Reparaturbetriebe dessen, was, Die größte Herausforderung für Köln und auch für andere Großstädte mit angespanntem Wohnungsmarkt, ist die Unterbringung der Menschen.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -911,25 +901,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B524E0C2-E715-414A-B65C-D84A8BCC95CF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="252" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F8398F-ACF3-42F9-9228-F1CBE1BEB6D7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -939,7 +910,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="392" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -948,7 +919,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF1DD58-4669-43E0-839F-4C49A776A038}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -958,7 +929,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -967,7 +938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321AC828-CA52-4D30-9A36-854D6436B639}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -977,7 +948,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="182" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -986,7 +957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
@@ -1017,13 +988,13 @@
     </row>
     <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
